--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1282,6 +1282,403 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129352638</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90280</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>970</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bittermusseron</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leucopaxillus gentianeus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Quél.) Kotl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Byrum, Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>620082</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6346069</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Julien Hach</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Julien Hach, Karin Hjelmér</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129352697</v>
+      </c>
+      <c r="B8" t="n">
+        <v>86841</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>424</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Byrum, Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>620115</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6346065</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Julien Hach</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Julien Hach, Karin Hjelmér</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129352715</v>
+      </c>
+      <c r="B9" t="n">
+        <v>87023</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Byrum, Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>620116</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6346113</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Julien Hach</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Julien Hach, Karin Hjelmér</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129352702</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91530</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>881</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skillerticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Inonotus cuticularis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Bull.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Byrum, Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>620074</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6346087</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Julien Hach</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Julien Hach, Karin Hjelmér</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>129352638</v>
       </c>
       <c r="B7" t="n">
-        <v>90280</v>
+        <v>90281</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>129352697</v>
       </c>
       <c r="B8" t="n">
-        <v>86841</v>
+        <v>86842</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>129352715</v>
       </c>
       <c r="B9" t="n">
-        <v>87023</v>
+        <v>87024</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>129352702</v>
       </c>
       <c r="B10" t="n">
-        <v>91530</v>
+        <v>91528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>129352638</v>
       </c>
       <c r="B7" t="n">
-        <v>90281</v>
+        <v>90284</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>129352697</v>
       </c>
       <c r="B8" t="n">
-        <v>86842</v>
+        <v>86845</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>129352715</v>
       </c>
       <c r="B9" t="n">
-        <v>87024</v>
+        <v>87027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>129352702</v>
       </c>
       <c r="B10" t="n">
-        <v>91528</v>
+        <v>91531</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>129352638</v>
       </c>
       <c r="B7" t="n">
-        <v>90284</v>
+        <v>90286</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>129352697</v>
       </c>
       <c r="B8" t="n">
-        <v>86845</v>
+        <v>86847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>129352715</v>
       </c>
       <c r="B9" t="n">
-        <v>87027</v>
+        <v>87029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>129352702</v>
       </c>
       <c r="B10" t="n">
-        <v>91531</v>
+        <v>91533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>129352638</v>
       </c>
       <c r="B7" t="n">
-        <v>90286</v>
+        <v>90290</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>129352697</v>
       </c>
       <c r="B8" t="n">
-        <v>86847</v>
+        <v>86851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>129352715</v>
       </c>
       <c r="B9" t="n">
-        <v>87029</v>
+        <v>87033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>129352702</v>
       </c>
       <c r="B10" t="n">
-        <v>91533</v>
+        <v>91537</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>129352638</v>
       </c>
       <c r="B7" t="n">
-        <v>90290</v>
+        <v>90291</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>129352697</v>
       </c>
       <c r="B8" t="n">
-        <v>86851</v>
+        <v>86852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>129352715</v>
       </c>
       <c r="B9" t="n">
-        <v>87033</v>
+        <v>87034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>129352702</v>
       </c>
       <c r="B10" t="n">
-        <v>91537</v>
+        <v>91538</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1679,6 +1679,108 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129540854</v>
+      </c>
+      <c r="B11" t="n">
+        <v>86921</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Byrum, Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>620133</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6346064</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Julien Hach</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Julien Hach, Martin Peraic</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>129352638</v>
       </c>
       <c r="B7" t="n">
-        <v>90291</v>
+        <v>90295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>129352702</v>
       </c>
       <c r="B10" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>129352638</v>
       </c>
       <c r="B7" t="n">
-        <v>90295</v>
+        <v>90323</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>129352697</v>
       </c>
       <c r="B8" t="n">
-        <v>86852</v>
+        <v>86880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>129352715</v>
       </c>
       <c r="B9" t="n">
-        <v>87034</v>
+        <v>87062</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>129352702</v>
       </c>
       <c r="B10" t="n">
-        <v>91541</v>
+        <v>91569</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>129540854</v>
       </c>
       <c r="B11" t="n">
-        <v>86921</v>
+        <v>86949</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>129352638</v>
       </c>
       <c r="B7" t="n">
-        <v>90323</v>
+        <v>90329</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>129352697</v>
       </c>
       <c r="B8" t="n">
-        <v>86880</v>
+        <v>86886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>129352715</v>
       </c>
       <c r="B9" t="n">
-        <v>87062</v>
+        <v>87068</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>129352702</v>
       </c>
       <c r="B10" t="n">
-        <v>91569</v>
+        <v>91575</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>129540854</v>
       </c>
       <c r="B11" t="n">
-        <v>86949</v>
+        <v>86955</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>129352638</v>
       </c>
       <c r="B7" t="n">
-        <v>90329</v>
+        <v>90330</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>129352697</v>
       </c>
       <c r="B8" t="n">
-        <v>86886</v>
+        <v>86887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>129352715</v>
       </c>
       <c r="B9" t="n">
-        <v>87068</v>
+        <v>87069</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>129352702</v>
       </c>
       <c r="B10" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>129540854</v>
       </c>
       <c r="B11" t="n">
-        <v>86955</v>
+        <v>86956</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>129352638</v>
       </c>
       <c r="B7" t="n">
-        <v>90330</v>
+        <v>90335</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>129352697</v>
       </c>
       <c r="B8" t="n">
-        <v>86887</v>
+        <v>86892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>129352715</v>
       </c>
       <c r="B9" t="n">
-        <v>87069</v>
+        <v>87074</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>129352702</v>
       </c>
       <c r="B10" t="n">
-        <v>91576</v>
+        <v>91581</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>129540854</v>
       </c>
       <c r="B11" t="n">
-        <v>86956</v>
+        <v>86961</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>129540854</v>
       </c>
       <c r="B11" t="n">
-        <v>86961</v>
+        <v>86965</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>129540854</v>
       </c>
       <c r="B11" t="n">
-        <v>86965</v>
+        <v>86967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>129540854</v>
       </c>
       <c r="B11" t="n">
-        <v>86967</v>
+        <v>86970</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4945457</v>
+        <v>129352697</v>
       </c>
       <c r="B2" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>424</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bokhultet syd Skäftekärr, Öl</t>
+          <t>Byrum, Byrum, Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620151.0218306591</v>
+        <v>620115</v>
       </c>
       <c r="R2" t="n">
-        <v>6346041.581409459</v>
+        <v>6346065</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,36 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>bokskog vid kanal</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Julien Hach</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Håkan Lundkvist, Ulla-Britt Andersson, Tommy Knutsson, Lennart Johnsson, Ingrid Johnsson, Jan-Olof Petersson, Elna Hultqvist</t>
+          <t>Julien Hach, Karin Hjelmér</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96117342</v>
+        <v>96117276</v>
       </c>
       <c r="B3" t="n">
-        <v>85301</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3739</v>
+        <v>444</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Juvelspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius croceocaeruleus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers. : Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620152.9800299823</v>
+        <v>620153</v>
       </c>
       <c r="R3" t="n">
-        <v>6346030.268718311</v>
+        <v>6346030</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,28 +843,22 @@
           <t>2021-09-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -913,56 +882,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96117276</v>
+        <v>129352702</v>
       </c>
       <c r="B4" t="n">
-        <v>85092</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91897</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>444</v>
+        <v>881</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Juvelspindling</t>
+          <t>Skillerticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius croceocaeruleus</t>
+          <t>Inonotus cuticularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers. : Fr.) Fr.</t>
+          <t>(Bull.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skäftekärr S, bokhultet, Öl</t>
+          <t>Byrum, Byrum, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620152.9800299823</v>
+        <v>620074</v>
       </c>
       <c r="R4" t="n">
-        <v>6346030.268718311</v>
+        <v>6346087</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,22 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,84 +961,75 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Bokskogshult med äldre bok, ädelgran, weymouthtall kring kanal</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Julien Hach</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Knutsson, Mikael Jeppson</t>
+          <t>Julien Hach, Karin Hjelmér</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96118549</v>
+        <v>129352638</v>
       </c>
       <c r="B5" t="n">
-        <v>88845</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4188</v>
+        <v>970</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Quél.) Kotl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skäftekärr S, bokhultet, Öl</t>
+          <t>Byrum, Byrum, Öl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620152.9800299823</v>
+        <v>620082</v>
       </c>
       <c r="R5" t="n">
-        <v>6346030.268718311</v>
+        <v>6346069</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,22 +1053,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,43 +1067,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bokskogshult med äldre bok, ädelgran, weymouthtall kring kanal</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Julien Hach</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Knutsson, Mikael Jeppson</t>
+          <t>Julien Hach, Karin Hjelmér</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96117414</v>
+        <v>314963</v>
       </c>
       <c r="B6" t="n">
-        <v>87958</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90637</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1193,22 +1114,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skäftekärr S, bokhultet, Öl</t>
+          <t>1 km SV Skäftekärr, Öl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620152.9800299823</v>
+        <v>620156</v>
       </c>
       <c r="R6" t="n">
-        <v>6346030.268718311</v>
+        <v>6346073</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1232,22 +1150,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,85 +1164,67 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Bokskogshult med äldre bok, ädelgran, weymouthtall kring kanal</t>
-        </is>
-      </c>
+          <t>Bokskog vid bruksväg</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Tommy Knutsson</t>
-        </is>
-      </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tommy Knutsson, Mikael Jeppson</t>
+          <t>Vera Wendt, Göran Wendt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129352638</v>
+        <v>314964</v>
       </c>
       <c r="B7" t="n">
-        <v>90335</v>
+        <v>90637</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Brödmusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Leucopaxillus tricolor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Peck) Kühner</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Byrum, Byrum, Öl</t>
+          <t>Bokhultet syd Skäftekärr, Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620082</v>
+        <v>620164</v>
       </c>
       <c r="R7" t="n">
-        <v>6346069</v>
+        <v>6346086</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1358,12 +1248,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,26 +1264,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>bokskog vid kanal</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Julien Hach</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Julien Hach, Karin Hjelmér</t>
+          <t>Thomas Gunnarsson, Jan-Olof Petersson, Lennart Johnsson, Ingrid Johnsson, Ulla-Britt Andersson, Tommy Knutsson, Håkan Lundkvist, Elna Hultqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129352697</v>
+        <v>96117414</v>
       </c>
       <c r="B8" t="n">
-        <v>86892</v>
+        <v>90637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,37 +1296,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>424</v>
+        <v>974</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Brödmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Leucopaxillus tricolor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Peck) Kühner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Byrum, Byrum, Öl</t>
+          <t>Skäftekärr S, bokhultet, Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620115</v>
+        <v>620153</v>
       </c>
       <c r="R8" t="n">
-        <v>6346065</v>
+        <v>6346030</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,12 +1353,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,28 +1367,38 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Bokskogshult med äldre bok, ädelgran, weymouthtall kring kanal</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Julien Hach</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Julien Hach, Karin Hjelmér</t>
+          <t>Tommy Knutsson, Mikael Jeppson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129352715</v>
+        <v>96117342</v>
       </c>
       <c r="B9" t="n">
-        <v>87074</v>
+        <v>87375</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,19 +1424,22 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Byrum, Byrum, Öl</t>
+          <t>Skäftekärr S, bokhultet, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620116</v>
+        <v>620153</v>
       </c>
       <c r="R9" t="n">
-        <v>6346113</v>
+        <v>6346030</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,12 +1463,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,50 +1477,56 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Bokskogshult med äldre bok, ädelgran, weymouthtall kring kanal</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Julien Hach</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Julien Hach, Karin Hjelmér</t>
+          <t>Tommy Knutsson, Mikael Jeppson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129352702</v>
+        <v>129352715</v>
       </c>
       <c r="B10" t="n">
-        <v>91581</v>
+        <v>87375</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>881</v>
+        <v>3739</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skillerticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Inonotus cuticularis</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bull.) P.Karst.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620074</v>
+        <v>620116</v>
       </c>
       <c r="R10" t="n">
-        <v>6346087</v>
+        <v>6346113</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,48 +1598,51 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129540854</v>
+        <v>96118549</v>
       </c>
       <c r="B11" t="n">
-        <v>86970</v>
+        <v>91322</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>248956</v>
+        <v>4188</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Byrum, Byrum, Öl</t>
+          <t>Skäftekärr S, bokhultet, Öl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620133</v>
+        <v>620153</v>
       </c>
       <c r="R11" t="n">
-        <v>6346064</v>
+        <v>6346030</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,12 +1666,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,26 +1680,653 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Bokskogshult med äldre bok, ädelgran, weymouthtall kring kanal</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Tommy Knutsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tommy Knutsson, Mikael Jeppson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2157760</v>
+      </c>
+      <c r="B12" t="n">
+        <v>111175</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bokhultet syd Skäftekärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>620164</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6346086</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2010-08-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2010-08-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>bokskog vid kanal</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Lennart Johnsson, Ingrid Johnsson, Håkan Lundkvist, Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>59519824</v>
+      </c>
+      <c r="B13" t="n">
+        <v>111175</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>bokskogen, Öl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>620154</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6346064</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2016-05-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2016-05-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Teresa Jonsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Teresa Jonsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2925640</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bokhultet syd Skäftekärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>620164</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6346086</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2010-08-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2010-08-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>bokskog vid kanal</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Lennart Johnsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Ingrid Johnsson, Håkan Lundkvist, Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4945457</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bokhultet syd Skäftekärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>620151</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6346042</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2010-08-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2010-08-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>bokskog vid kanal</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Håkan Lundkvist, Ulla-Britt Andersson, Tommy Knutsson, Lennart Johnsson, Ingrid Johnsson, Jan-Olof Petersson, Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129352710</v>
+      </c>
+      <c r="B16" t="n">
+        <v>87204</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>248952</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåfotad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cortinarius barbaricus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Brandrud) Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Byrum, Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>620142</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6346007</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Julien Hach</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Julien Hach, Karin Hjelmér</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129540854</v>
+      </c>
+      <c r="B17" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Byrum, Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>620133</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6346064</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Julien Hach</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Julien Hach, Martin Peraic</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2925640</v>
+        <v>135208553</v>
       </c>
       <c r="B14" t="n">
-        <v>99096</v>
+        <v>99170</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1925,42 +1925,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bokhultet syd Skäftekärr, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620164</v>
+        <v>620026</v>
       </c>
       <c r="R14" t="n">
-        <v>6346086</v>
+        <v>6346219</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1984,12 +1979,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 ex i knopp 1 m från beläggningskanten</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2000,35 +2000,30 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>bokskog vid kanal</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Lennart Johnsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Ingrid Johnsson, Håkan Lundkvist, Elna Hultqvist</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4945457</v>
+        <v>135208554</v>
       </c>
       <c r="B15" t="n">
-        <v>101325</v>
+        <v>99170</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,37 +2031,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>219797</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bokhultet syd Skäftekärr, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620151</v>
+        <v>620042</v>
       </c>
       <c r="R15" t="n">
-        <v>6346042</v>
+        <v>6346234</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2090,12 +2085,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 ex i knopp 1 m från beläggningskanten</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2106,73 +2106,73 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>bokskog vid kanal</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Håkan Lundkvist, Ulla-Britt Andersson, Tommy Knutsson, Lennart Johnsson, Ingrid Johnsson, Jan-Olof Petersson, Elna Hultqvist</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129352710</v>
+        <v>2925640</v>
       </c>
       <c r="B16" t="n">
-        <v>87204</v>
+        <v>99096</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>248952</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåfotad fagerspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius barbaricus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brandrud) Frøslev &amp; al.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Byrum, Byrum, Öl</t>
+          <t>Bokhultet syd Skäftekärr, Öl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620142</v>
+        <v>620164</v>
       </c>
       <c r="R16" t="n">
-        <v>6346007</v>
+        <v>6346086</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2196,12 +2196,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2212,64 +2212,73 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>bokskog vid kanal</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Julien Hach</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Julien Hach, Karin Hjelmér</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Thomas Gunnarsson, Lennart Johnsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Ingrid Johnsson, Håkan Lundkvist, Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129540854</v>
+        <v>4945457</v>
       </c>
       <c r="B17" t="n">
-        <v>87262</v>
+        <v>101325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>248956</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Byrum, Byrum, Öl</t>
+          <t>Bokhultet syd Skäftekärr, Öl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620133</v>
+        <v>620151</v>
       </c>
       <c r="R17" t="n">
-        <v>6346064</v>
+        <v>6346042</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2293,12 +2302,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2307,26 +2316,229 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>bokskog vid kanal</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Håkan Lundkvist, Ulla-Britt Andersson, Tommy Knutsson, Lennart Johnsson, Ingrid Johnsson, Jan-Olof Petersson, Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129352710</v>
+      </c>
+      <c r="B18" t="n">
+        <v>87204</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>248952</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåfotad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cortinarius barbaricus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Brandrud) Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Byrum, Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>620142</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6346007</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Julien Hach</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Julien Hach, Karin Hjelmér</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129540854</v>
+      </c>
+      <c r="B19" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Byrum, Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>620133</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6346064</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Julien Hach</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Julien Hach, Martin Peraic</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -2009,7 +2009,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edvin Åhman, Christine Sandberg</t>
+          <t>Christine Sandberg, Edvin Åhman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Edvin Åhman, Christine Sandberg</t>
+          <t>Christine Sandberg, Edvin Åhman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -2009,7 +2009,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Christine Sandberg, Edvin Åhman</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Christine Sandberg, Edvin Åhman</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129352697</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96117276</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129352702</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129352638</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/314963</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/314964</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,6 +1427,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96117414</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96117342</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1595,6 +1640,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129352715</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,6 +1751,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96118549</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1805,6 +1860,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2157760</t>
         </is>
       </c>
     </row>
@@ -1911,6 +1971,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59519824</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2017,6 +2082,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135208553</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2123,6 +2193,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135208554</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2234,6 +2309,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2925640</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2340,6 +2420,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4945457</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2437,6 +2522,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129352710</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2539,8 +2629,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129540854</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -1982,7 +1982,7 @@
         <v>135208553</v>
       </c>
       <c r="B14" t="n">
-        <v>99170</v>
+        <v>99217</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>135208554</v>
       </c>
       <c r="B15" t="n">
-        <v>99170</v>
+        <v>99217</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -1982,7 +1982,7 @@
         <v>135208553</v>
       </c>
       <c r="B14" t="n">
-        <v>99217</v>
+        <v>99244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>135208554</v>
       </c>
       <c r="B15" t="n">
-        <v>99217</v>
+        <v>99244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2925640</v>
+        <v>135208553</v>
       </c>
       <c r="B14" t="n">
-        <v>99096</v>
+        <v>99249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,42 +1990,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bokhultet syd Skäftekärr, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620164</v>
+        <v>620026</v>
       </c>
       <c r="R14" t="n">
-        <v>6346086</v>
+        <v>6346219</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2049,12 +2044,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 ex i knopp 1 m från beläggningskanten</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2065,40 +2065,35 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>bokskog vid kanal</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Lennart Johnsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Ingrid Johnsson, Håkan Lundkvist, Elna Hultqvist</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2925640</t>
+          <t>https://artportalen.se/Sighting/135208553</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4945457</v>
+        <v>135208554</v>
       </c>
       <c r="B15" t="n">
-        <v>101325</v>
+        <v>99249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,37 +2101,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>219797</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bokhultet syd Skäftekärr, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620151</v>
+        <v>620042</v>
       </c>
       <c r="R15" t="n">
-        <v>6346042</v>
+        <v>6346234</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2160,12 +2155,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 ex i knopp 1 m från beläggningskanten</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2176,78 +2176,78 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>bokskog vid kanal</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Håkan Lundkvist, Ulla-Britt Andersson, Tommy Knutsson, Lennart Johnsson, Ingrid Johnsson, Jan-Olof Petersson, Elna Hultqvist</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4945457</t>
+          <t>https://artportalen.se/Sighting/135208554</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129352710</v>
+        <v>2925640</v>
       </c>
       <c r="B16" t="n">
-        <v>87204</v>
+        <v>99096</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>248952</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåfotad fagerspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius barbaricus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brandrud) Frøslev &amp; al.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Byrum, Byrum, Öl</t>
+          <t>Bokhultet syd Skäftekärr, Öl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620142</v>
+        <v>620164</v>
       </c>
       <c r="R16" t="n">
-        <v>6346007</v>
+        <v>6346086</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2287,69 +2287,78 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>bokskog vid kanal</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Julien Hach</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Julien Hach, Karin Hjelmér</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Thomas Gunnarsson, Lennart Johnsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Ingrid Johnsson, Håkan Lundkvist, Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129352710</t>
+          <t>https://artportalen.se/Sighting/2925640</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129540854</v>
+        <v>4945457</v>
       </c>
       <c r="B17" t="n">
-        <v>87262</v>
+        <v>101325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>248956</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Byrum, Byrum, Öl</t>
+          <t>Bokhultet syd Skäftekärr, Öl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620133</v>
+        <v>620151</v>
       </c>
       <c r="R17" t="n">
-        <v>6346064</v>
+        <v>6346042</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2373,12 +2382,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,27 +2396,240 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>bokskog vid kanal</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Håkan Lundkvist, Ulla-Britt Andersson, Tommy Knutsson, Lennart Johnsson, Ingrid Johnsson, Jan-Olof Petersson, Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4945457</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129352710</v>
+      </c>
+      <c r="B18" t="n">
+        <v>87204</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>248952</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåfotad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cortinarius barbaricus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Brandrud) Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Byrum, Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>620142</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6346007</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Julien Hach</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Julien Hach, Karin Hjelmér</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129352710</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129540854</v>
+      </c>
+      <c r="B19" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Byrum, Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>620133</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6346064</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Julien Hach</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Julien Hach, Martin Peraic</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129540854</t>
         </is>
@@ -2431,6 +2653,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -1982,7 +1982,7 @@
         <v>135208553</v>
       </c>
       <c r="B14" t="n">
-        <v>99249</v>
+        <v>99251</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>135208554</v>
       </c>
       <c r="B15" t="n">
-        <v>99249</v>
+        <v>99251</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
